--- a/data/trans_orig/Q03B_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q03B_R-Clase-trans_orig.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,48</t>
+          <t>1,19; 1,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,22 +687,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,03</t>
+          <t>1,76; 2,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 2,98</t>
+          <t>2,59; 3,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,42</t>
+          <t>3,0; 3,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,24</t>
+          <t>2,87; 3,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 2,34</t>
+          <t>2,06; 2,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 2,53</t>
+          <t>2,3; 2,52</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,56</t>
+          <t>1,21; 1,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 1,83</t>
+          <t>1,55; 1,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,46</t>
+          <t>3,05; 3,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 3,67</t>
+          <t>3,22; 3,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,17 +817,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,46</t>
+          <t>2,15; 2,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 2,6</t>
+          <t>2,32; 2,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 2,7</t>
+          <t>2,44; 2,71</t>
         </is>
       </c>
     </row>
@@ -897,32 +897,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,67</t>
+          <t>1,29; 1,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,75</t>
+          <t>1,51; 1,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,92</t>
+          <t>1,67; 1,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 4,31</t>
+          <t>3,59; 4,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,79</t>
+          <t>3,26; 3,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,78</t>
+          <t>3,15; 3,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 2,32</t>
+          <t>2,04; 2,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 2,35</t>
+          <t>2,06; 2,34</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,52</t>
+          <t>1,34; 1,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 1,81</t>
+          <t>1,6; 1,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 3,8</t>
+          <t>3,45; 3,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 3,86</t>
+          <t>3,58; 3,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,56</t>
+          <t>3,3; 3,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 2,28</t>
+          <t>2,05; 2,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 2,43</t>
+          <t>2,25; 2,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 2,52</t>
+          <t>2,34; 2,52</t>
         </is>
       </c>
     </row>
@@ -1117,42 +1117,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,33</t>
+          <t>0,98; 1,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,59</t>
+          <t>1,31; 1,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,75</t>
+          <t>1,52; 1,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 4,48</t>
+          <t>4,04; 4,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 4,08</t>
+          <t>3,74; 4,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 4,11</t>
+          <t>3,79; 4,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 3,24</t>
+          <t>2,9; 3,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 3,07</t>
+          <t>2,81; 3,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1232,42 +1232,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,03</t>
+          <t>0,69; 1,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,36</t>
+          <t>1,08; 1,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 3,57</t>
+          <t>3,3; 3,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,07; 3,34</t>
+          <t>3,08; 3,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 3,45</t>
+          <t>3,2; 3,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,03</t>
+          <t>2,77; 3,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 2,88</t>
+          <t>2,63; 2,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 3,02</t>
+          <t>2,77; 3,0</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 1,74</t>
+          <t>1,65; 1,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 3,64</t>
+          <t>3,47; 3,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 3,58</t>
+          <t>3,44; 3,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 2,49</t>
+          <t>2,36; 2,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 2,56</t>
+          <t>2,45; 2,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 2,66</t>
+          <t>2,56; 2,66</t>
         </is>
       </c>
     </row>
